--- a/OUTPUT/gate_oof/fold_3/inner_fold_audit.xlsx
+++ b/OUTPUT/gate_oof/fold_3/inner_fold_audit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>21.79535639999995</v>
+        <v>15.33059010002762</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>27.2039120999998</v>
+        <v>17.16540379996877</v>
       </c>
     </row>
     <row r="4">
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>41.47449799999958</v>
+        <v>16.49328739999328</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>44.18277560000024</v>
+        <v>15.82845679996535</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>43.14561890000004</v>
+        <v>179.7395167000359</v>
       </c>
     </row>
   </sheetData>
